--- a/data/trans_orig/P36BPD09_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48998</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24085</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43779</t>
+          <t>44553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52379</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84329</t>
+          <t>83364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322094</t>
+          <t>320025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365641</t>
+          <t>364613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269375</t>
+          <t>270492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304456</t>
+          <t>304672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>604363</t>
+          <t>602959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>658922</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108446</t>
+          <t>106847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149099</t>
+          <t>148716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110213</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143920</t>
+          <t>143411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229696</t>
+          <t>230413</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280995</t>
+          <t>283124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>51249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81304</t>
+          <t>80343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>295885</t>
+          <t>295051</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>337411</t>
+          <t>336248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>245749</t>
+          <t>245202</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276801</t>
+          <t>276247</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>552459</t>
+          <t>552933</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>603047</t>
+          <t>603294</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,27%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82687</t>
+          <t>83011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120847</t>
+          <t>122414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75392</t>
+          <t>76102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104024</t>
+          <t>104870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166745</t>
+          <t>168127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215824</t>
+          <t>214424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45129</t>
+          <t>46524</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>53138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100161</t>
+          <t>111720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>442346</t>
+          <t>442758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87500</t>
+          <t>88020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108808</t>
+          <t>107658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152695</t>
+          <t>142870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536831</t>
+          <t>536750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182401</t>
+          <t>182371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556224</t>
+          <t>546752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>51111</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70498</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247798</t>
+          <t>248856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>660022</t>
+          <t>670238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61136</t>
+          <t>60994</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107759</t>
+          <t>103489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>64054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85401</t>
+          <t>90534</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154613</t>
+          <t>154955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>633795</t>
+          <t>635281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>701891</t>
+          <t>702453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>284613</t>
+          <t>277246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>693175</t>
+          <t>691094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>828481</t>
+          <t>854668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1359971</t>
+          <t>1358788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>257902</t>
+          <t>256735</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>320491</t>
+          <t>316675</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227611</t>
+          <t>229266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>668619</t>
+          <t>674680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>515853</t>
+          <t>514350</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1112571</t>
+          <t>1075107</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56619</t>
+          <t>55868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60507</t>
+          <t>61923</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>70471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110263</t>
+          <t>111810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>258071</t>
+          <t>258516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>305845</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>445549</t>
+          <t>437575</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>584470</t>
+          <t>579857</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>720144</t>
+          <t>722287</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>869254</t>
+          <t>868709</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,22%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>128943</t>
+          <t>129907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171881</t>
+          <t>172669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224156</t>
+          <t>224570</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>351065</t>
+          <t>356195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>369596</t>
+          <t>371150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>509409</t>
+          <t>502342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36723</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53856</t>
+          <t>53471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84571</t>
+          <t>84997</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67287</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108692</t>
+          <t>109686</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>148931</t>
+          <t>149342</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193153</t>
+          <t>194493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>481427</t>
+          <t>480377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>528711</t>
+          <t>529730</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>649612</t>
+          <t>647210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>714075</t>
+          <t>713279</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29608</t>
+          <t>31063</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73322</t>
+          <t>73123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164908</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>206491</t>
+          <t>207989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>206293</t>
+          <t>206082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264865</t>
+          <t>264209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>177035</t>
+          <t>178716</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>270675</t>
+          <t>273087</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192823</t>
+          <t>188761</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>272047</t>
+          <t>267719</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>398454</t>
+          <t>402462</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>519706</t>
+          <t>519618</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1601493</t>
+          <t>1543992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2236843</t>
+          <t>2240659</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1784979</t>
+          <t>1752565</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2360650</t>
+          <t>2360489</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3648090</t>
+          <t>3696885</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4529398</t>
+          <t>4542845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>886361</t>
+          <t>885284</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1587050</t>
+          <t>1684398</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>965381</t>
+          <t>970595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1592540</t>
+          <t>1650524</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1915922</t>
+          <t>1903855</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2927552</t>
+          <t>2839983</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD09_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>39522</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47428</t>
+          <t>56590</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>39878</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>29974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44553</t>
+          <t>53036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>67047</t>
+          <t>79400</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52632</t>
+          <t>63029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>97468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>343725</t>
+          <t>369406</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320025</t>
+          <t>344476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364613</t>
+          <t>392235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>287384</t>
+          <t>308940</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270492</t>
+          <t>291085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304672</t>
+          <t>328774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>631108</t>
+          <t>678346</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>602959</t>
+          <t>648462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>707363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>128122</t>
+          <t>141691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>120685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148716</t>
+          <t>164503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>139593</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110213</t>
+          <t>121350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143411</t>
+          <t>158008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>254524</t>
+          <t>281283</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230413</t>
+          <t>256347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283124</t>
+          <t>311436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>25590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46910</t>
+          <t>48714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31930</t>
+          <t>35850</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42692</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>65659</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51249</t>
+          <t>57490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80343</t>
+          <t>90525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>316737</t>
+          <t>334299</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>295051</t>
+          <t>312414</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>336248</t>
+          <t>356914</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>261184</t>
+          <t>287438</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>245202</t>
+          <t>270431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276247</t>
+          <t>302330</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>577921</t>
+          <t>621737</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>552933</t>
+          <t>593523</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>603294</t>
+          <t>651053</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>101747</t>
+          <t>112424</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83011</t>
+          <t>94243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122414</t>
+          <t>135320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89466</t>
+          <t>99855</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>86141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104870</t>
+          <t>114503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>191214</t>
+          <t>212278</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168127</t>
+          <t>185276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214424</t>
+          <t>239864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46524</t>
+          <t>41828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>32977</t>
+          <t>37199</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>26681</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53138</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>273608</t>
+          <t>304713</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111720</t>
+          <t>283582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>442758</t>
+          <t>326092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>98352</t>
+          <t>111759</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88020</t>
+          <t>99849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107658</t>
+          <t>122227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>371960</t>
+          <t>416472</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142870</t>
+          <t>393372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536750</t>
+          <t>441128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>366786</t>
+          <t>135377</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182371</t>
+          <t>114546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546752</t>
+          <t>155265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60514</t>
+          <t>67191</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>56259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>78698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>427300</t>
+          <t>202567</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248856</t>
+          <t>180252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>670238</t>
+          <t>228226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>665892</t>
+          <t>469309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>665892</t>
+          <t>469309</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>665892</t>
+          <t>469309</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>832237</t>
+          <t>656238</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>832237</t>
+          <t>656238</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>832237</t>
+          <t>656238</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>92984</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>72608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103489</t>
+          <t>117458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45464</t>
+          <t>54764</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>43328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64054</t>
+          <t>68445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>124653</t>
+          <t>147749</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90534</t>
+          <t>122913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154955</t>
+          <t>177758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>718729</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>635281</t>
+          <t>682932</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>702453</t>
+          <t>752862</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>541099</t>
+          <t>599402</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>277246</t>
+          <t>576345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>691094</t>
+          <t>622035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1209364</t>
+          <t>1318131</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>854668</t>
+          <t>1272942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1358788</t>
+          <t>1361636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>286732</t>
+          <t>319463</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>256735</t>
+          <t>286942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316675</t>
+          <t>352139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>390966</t>
+          <t>206474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>229266</t>
+          <t>185191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>674680</t>
+          <t>228663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>677698</t>
+          <t>525937</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>514350</t>
+          <t>488319</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1075107</t>
+          <t>568686</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034186</t>
+          <t>1131177</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034186</t>
+          <t>1131177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034186</t>
+          <t>1131177</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2011715</t>
+          <t>1991817</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2011715</t>
+          <t>1991817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2011715</t>
+          <t>1991817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>41600</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28456</t>
+          <t>33722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55868</t>
+          <t>65480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>53774</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>43032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61923</t>
+          <t>66023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>100891</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70471</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111810</t>
+          <t>123602</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>281707</t>
+          <t>342047</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>258516</t>
+          <t>314354</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>305845</t>
+          <t>365892</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>501203</t>
+          <t>492288</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>437575</t>
+          <t>467027</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>579857</t>
+          <t>516132</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>782910</t>
+          <t>834335</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>722287</t>
+          <t>798669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>868709</t>
+          <t>867764</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>150029</t>
+          <t>176942</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129907</t>
+          <t>155173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172669</t>
+          <t>202253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>288949</t>
+          <t>282030</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224570</t>
+          <t>259724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>356195</t>
+          <t>306193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>438978</t>
+          <t>458972</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>371150</t>
+          <t>425756</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>502342</t>
+          <t>489758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473336</t>
+          <t>566106</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473336</t>
+          <t>566106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473336</t>
+          <t>566106</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>838590</t>
+          <t>828092</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>838590</t>
+          <t>828092</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>838590</t>
+          <t>828092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1311927</t>
+          <t>1394198</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1311927</t>
+          <t>1394198</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1311927</t>
+          <t>1394198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>37691</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66972</t>
+          <t>76651</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>58445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>96855</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>85172</t>
+          <t>96280</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66488</t>
+          <t>75857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109686</t>
+          <t>120379</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>173330</t>
+          <t>172707</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>149342</t>
+          <t>149814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194493</t>
+          <t>191991</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>507006</t>
+          <t>559697</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>480377</t>
+          <t>530498</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>529730</t>
+          <t>585364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>680336</t>
+          <t>732405</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>647210</t>
+          <t>695006</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>713279</t>
+          <t>766211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>48978</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31063</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73123</t>
+          <t>65625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,22 +3266,22 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>184606</t>
+          <t>205173</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164992</t>
+          <t>183009</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>207989</t>
+          <t>229988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>233584</t>
+          <t>250064</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>206082</t>
+          <t>221913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264209</t>
+          <t>282573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>758584</t>
+          <t>841521</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>758584</t>
+          <t>841521</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>758584</t>
+          <t>841521</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>999092</t>
+          <t>1078749</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>999092</t>
+          <t>1078749</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>999092</t>
+          <t>1078749</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>231582</t>
+          <t>264961</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178716</t>
+          <t>229580</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>273087</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>233964</t>
+          <t>268898</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>188761</t>
+          <t>241335</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>267719</t>
+          <t>300416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>465546</t>
+          <t>533858</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>402462</t>
+          <t>487663</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>519618</t>
+          <t>581580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2057371</t>
+          <t>2241901</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1543992</t>
+          <t>2181062</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2240659</t>
+          <t>2303940</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2196229</t>
+          <t>2359523</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1752565</t>
+          <t>2310154</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2360489</t>
+          <t>2414403</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4253599</t>
+          <t>4601424</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3696885</t>
+          <t>4521273</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4542845</t>
+          <t>4685020</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1082394</t>
+          <t>930788</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>885284</t>
+          <t>873213</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1684398</t>
+          <t>985916</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1140903</t>
+          <t>1000314</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>970595</t>
+          <t>951006</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1650524</t>
+          <t>1049653</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2223297</t>
+          <t>1931102</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1903855</t>
+          <t>1857737</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2839983</t>
+          <t>2006107</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3371347</t>
+          <t>3437650</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3371347</t>
+          <t>3437650</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3371347</t>
+          <t>3437650</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3571096</t>
+          <t>3628735</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3571096</t>
+          <t>3628735</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3571096</t>
+          <t>3628735</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6942442</t>
+          <t>7066385</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6942442</t>
+          <t>7066385</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6942442</t>
+          <t>7066385</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
